--- a/data-raw/bacen_codes.xlsx
+++ b/data-raw/bacen_codes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/viniciusreginatto/GitHub/realestatebr/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9F1542-6CEF-A840-9AA2-735BB06BB25C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D677D78F-6070-8341-B067-D0B1266898CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1320" windowWidth="28800" windowHeight="15760" xr2:uid="{0BDEE7C6-332B-4F5C-8740-144CDD417F7B}"/>
   </bookViews>
@@ -1086,61 +1086,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1244,6 +1189,25 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
         <family val="2"/>
@@ -1269,6 +1233,42 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1661,20 +1661,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{185383FF-D0E6-254B-BCD7-37532E0B548E}" name="Table1" displayName="Table1" ref="A1:H142" totalsRowShown="0" headerRowDxfId="1" dataDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{185383FF-D0E6-254B-BCD7-37532E0B548E}" name="Table1" displayName="Table1" ref="A1:H142" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A1:H142" xr:uid="{185383FF-D0E6-254B-BCD7-37532E0B548E}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H141">
-    <sortCondition ref="H1:H141"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H142">
+    <sortCondition ref="H1:H142"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{7E437DD1-BC46-4748-ACC0-7F43AF1FF1E1}" name="code_bcb" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{C3C80F59-5F47-B041-BCC6-2C93AA964C63}" name="bcb_category" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{06792841-D349-4F4B-B4BE-E3FB584C4C41}" name="bcb_subcategory" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{A4348D0C-0970-0447-98E4-AB0ACD5515CB}" name="name_simplified" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{275E25A1-C18E-7241-9BE6-E6F10BE08049}" name="name_full" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{BEDD992D-2950-7B4A-8B64-3CB6AB756CC0}" name="unit" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{E617C974-1C03-9F49-9DC7-137E90C099AA}" name="frequency" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{67A6F963-9FCE-AD49-B3AB-B6B3B5EB412B}" name="hierarchy" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{7E437DD1-BC46-4748-ACC0-7F43AF1FF1E1}" name="code_bcb" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C3C80F59-5F47-B041-BCC6-2C93AA964C63}" name="bcb_category" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{06792841-D349-4F4B-B4BE-E3FB584C4C41}" name="bcb_subcategory" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{A4348D0C-0970-0447-98E4-AB0ACD5515CB}" name="name_simplified" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{275E25A1-C18E-7241-9BE6-E6F10BE08049}" name="name_full" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{BEDD992D-2950-7B4A-8B64-3CB6AB756CC0}" name="unit" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{E617C974-1C03-9F49-9DC7-137E90C099AA}" name="frequency" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{67A6F963-9FCE-AD49-B3AB-B6B3B5EB412B}" name="hierarchy" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2018,7 +2018,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="5">
-        <v>606</v>
+        <v>20690</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>323</v>
@@ -2027,24 +2027,24 @@
         <v>318</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H2" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A3" s="5">
-        <v>619</v>
+        <v>20691</v>
       </c>
       <c r="B3" s="11" t="s">
         <v>323</v>
@@ -2053,19 +2053,19 @@
         <v>318</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>20704</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="5">
-        <v>632</v>
+        <v>20692</v>
       </c>
       <c r="B4" s="11" t="s">
         <v>323</v>
@@ -2082,19 +2082,19 @@
         <v>318</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H4" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M4" s="1">
         <v>20756</v>
@@ -2102,7 +2102,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="5">
-        <v>645</v>
+        <v>20702</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>323</v>
@@ -2111,19 +2111,19 @@
         <v>318</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H5" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M5" s="1">
         <v>20768</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="5">
-        <v>918</v>
+        <v>20703</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>323</v>
@@ -2140,19 +2140,19 @@
         <v>318</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H6" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>20914</v>
@@ -2160,7 +2160,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="5">
-        <v>931</v>
+        <v>20704</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>323</v>
@@ -2169,106 +2169,106 @@
         <v>318</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M7" s="1">
         <v>21072</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A8" s="5">
-        <v>944</v>
+      <c r="A8" s="1">
+        <v>20756</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H8" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M8" s="5">
         <v>21084</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A9" s="5">
-        <v>957</v>
+      <c r="A9" s="1">
+        <v>20763</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H9" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M9" s="5">
         <v>21340</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A10" s="5">
-        <v>3986</v>
+      <c r="A10" s="1">
+        <v>20774</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H10" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M10" s="5">
         <v>24364</v>
@@ -2276,22 +2276,22 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A11" s="5">
-        <v>20690</v>
+        <v>20902</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>2</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A12" s="5">
-        <v>20691</v>
+        <v>20914</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>2</v>
@@ -2333,25 +2333,25 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A13" s="5">
-        <v>20692</v>
+      <c r="A13" s="1">
+        <v>21058</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H13" s="5">
@@ -2362,25 +2362,25 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A14" s="5">
-        <v>20702</v>
+      <c r="A14" s="1">
+        <v>21059</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H14" s="5">
@@ -2388,25 +2388,25 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A15" s="5">
-        <v>20703</v>
+      <c r="A15" s="1">
+        <v>21060</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H15" s="5">
@@ -2414,25 +2414,25 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.15">
-      <c r="A16" s="5">
-        <v>20704</v>
+      <c r="A16" s="1">
+        <v>21070</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G16" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H16" s="5">
@@ -2441,22 +2441,22 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
-        <v>20756</v>
+        <v>21071</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>225</v>
+        <v>320</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>2</v>
@@ -2467,362 +2467,362 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
-        <v>20757</v>
+        <v>21072</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C18" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A19" s="5">
+        <v>21132</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A20" s="5">
+        <v>21133</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A21" s="5">
+        <v>21139</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A22" s="5">
+        <v>21145</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A23" s="5">
+        <v>21151</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A24" s="2">
+        <v>25351</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="D24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H18" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A19" s="1">
-        <v>20761</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C19" s="11" t="s">
+      <c r="G24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A25" s="2">
+        <v>25357</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="D25" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H19" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A20" s="1">
-        <v>20762</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C20" s="11" t="s">
+      <c r="G25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A26" s="2">
+        <v>25359</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F20" s="1" t="s">
+      <c r="D26" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A21" s="1">
-        <v>20763</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C21" s="11" t="s">
+      <c r="G26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A27" s="2">
+        <v>27713</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="D27" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H21" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A22" s="1">
-        <v>20768</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="G27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A28" s="2">
+        <v>27714</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="D28" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H22" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A23" s="1">
-        <v>20772</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C23" s="11" t="s">
+      <c r="G28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A29" s="2">
+        <v>27715</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="F23" s="1" t="s">
+      <c r="D29" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H23" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A24" s="1">
-        <v>20773</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H24" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A25" s="1">
-        <v>20774</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H25" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A26" s="5">
-        <v>20900</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H26" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A27" s="5">
-        <v>20901</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H27" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A28" s="5">
-        <v>20902</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H28" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A29" s="5">
-        <v>20912</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G29" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H29" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A30" s="5">
-        <v>20913</v>
+      <c r="A30" s="1">
+        <v>29033</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H30" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A31" s="5">
-        <v>20914</v>
+      <c r="A31" s="1">
+        <v>29034</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G31" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H31" s="5">
@@ -2831,19 +2831,19 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
-        <v>21053</v>
+        <v>29035</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>237</v>
+        <v>322</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>1</v>
@@ -2852,24 +2852,24 @@
         <v>2</v>
       </c>
       <c r="H32" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
-        <v>21054</v>
+        <v>29036</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>238</v>
+        <v>322</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>1</v>
@@ -2878,24 +2878,24 @@
         <v>2</v>
       </c>
       <c r="H33" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
-        <v>21058</v>
+        <v>29037</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>239</v>
+        <v>322</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>1</v>
@@ -2909,19 +2909,19 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
-        <v>21059</v>
+        <v>29038</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>240</v>
+        <v>322</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>1</v>
@@ -2934,25 +2934,23 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A36" s="1">
-        <v>21060</v>
+      <c r="A36" s="5">
+        <v>21340</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>320</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C36" s="11"/>
       <c r="D36" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H36" s="5">
@@ -2960,51 +2958,47 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A37" s="1">
-        <v>21066</v>
+      <c r="A37" s="5">
+        <v>432</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>320</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C37" s="11"/>
       <c r="D37" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>2</v>
+        <v>80</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="H37" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A38" s="1">
-        <v>21070</v>
+      <c r="A38" s="5">
+        <v>13421</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>320</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="C38" s="11"/>
       <c r="D38" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H38" s="5">
@@ -3013,24 +3007,22 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>21071</v>
+        <v>189</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>320</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C39" s="11"/>
       <c r="D39" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G39" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G39" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H39" s="5">
@@ -3038,25 +3030,23 @@
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A40" s="1">
-        <v>21072</v>
+      <c r="A40" s="5">
+        <v>192</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>320</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C40" s="11"/>
       <c r="D40" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H40" s="5">
@@ -3065,50 +3055,48 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A41" s="5">
-        <v>21082</v>
+        <v>433</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>321</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C41" s="11"/>
       <c r="D41" s="2" t="s">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>4</v>
+        <v>104</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H41" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A42" s="5">
-        <v>21083</v>
+      <c r="A42" s="1">
+        <v>20757</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G42" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H42" s="5">
@@ -3116,25 +3104,25 @@
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A43" s="5">
-        <v>21084</v>
+      <c r="A43" s="1">
+        <v>20761</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G43" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H43" s="5">
@@ -3142,682 +3130,676 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A44" s="5">
-        <v>21132</v>
+      <c r="A44" s="1">
+        <v>20762</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G44" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H44" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A45" s="5">
-        <v>21133</v>
+      <c r="A45" s="1">
+        <v>20768</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G45" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H45" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A46" s="5">
-        <v>21139</v>
+      <c r="A46" s="1">
+        <v>20772</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G46" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H46" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A47" s="5">
-        <v>21145</v>
+      <c r="A47" s="1">
+        <v>20773</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G47" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G47" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H47" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A48" s="5">
-        <v>21151</v>
+        <v>20900</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>323</v>
       </c>
       <c r="C48" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H48" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A49" s="5">
+        <v>20901</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H49" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A50" s="5">
+        <v>20912</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H50" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A51" s="5">
+        <v>20913</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A52" s="1">
+        <v>21053</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A53" s="1">
+        <v>21054</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H53" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A54" s="1">
+        <v>21066</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A55" s="5">
+        <v>21082</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C55" s="11" t="s">
         <v>321</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H48" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A49" s="2">
-        <v>25351</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C49" s="2" t="s">
+      <c r="D55" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A56" s="5">
+        <v>21083</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H56" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A57" s="5">
+        <v>21084</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H57" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A58" s="2">
+        <v>25358</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="F49" s="2" t="s">
+      <c r="D58" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H49" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A50" s="2">
-        <v>25357</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H50" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A51" s="2">
-        <v>25358</v>
-      </c>
-      <c r="B51" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H51" s="5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A52" s="2">
-        <v>25359</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H52" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A53" s="2">
-        <v>27713</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H53" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A54" s="2">
-        <v>27714</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H54" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A55" s="2">
-        <v>27715</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H55" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A56" s="1">
-        <v>29033</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H56" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A57" s="1">
-        <v>29034</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H57" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A58" s="1">
-        <v>29035</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H58" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A59" s="1">
-        <v>29036</v>
+      <c r="A59" s="2">
+        <v>1636</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G59" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" s="11"/>
+      <c r="D59" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H59" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A60" s="1">
-        <v>29037</v>
+      <c r="A60" s="2">
+        <v>1645</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G60" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="11"/>
+      <c r="D60" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G60" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H60" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A61" s="1">
-        <v>29038</v>
+      <c r="A61" s="5">
+        <v>2144</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C61" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C61" s="11"/>
+      <c r="D61" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H61" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="5">
-        <v>21340</v>
+        <v>2147</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="2" t="s">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>7</v>
+        <v>108</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H62" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="5">
-        <v>432</v>
+        <v>2148</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="H63" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="5">
-        <v>13421</v>
+        <v>4003</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="2" t="s">
-        <v>42</v>
+        <v>155</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>43</v>
+        <v>154</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H64" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A65" s="1">
-        <v>189</v>
+      <c r="A65" s="5">
+        <v>4007</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="2" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H65" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A66" s="5">
-        <v>192</v>
+        <v>4010</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="2" t="s">
-        <v>39</v>
+        <v>118</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H66" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A67" s="5">
-        <v>433</v>
+        <v>4011</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="2" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H67" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A68" s="2">
-        <v>1636</v>
+      <c r="A68" s="5">
+        <v>4016</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="2" t="s">
-        <v>196</v>
+        <v>122</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H68" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A69" s="2">
-        <v>1645</v>
+      <c r="A69" s="5">
+        <v>4040</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="2" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>195</v>
+        <v>123</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H69" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A70" s="5">
-        <v>2144</v>
+        <v>4043</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="2" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>108</v>
@@ -3832,17 +3814,17 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A71" s="5">
-        <v>2147</v>
+        <v>4044</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="2" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>108</v>
@@ -3857,17 +3839,17 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A72" s="5">
-        <v>2148</v>
+        <v>4049</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>108</v>
@@ -3882,17 +3864,17 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A73" s="5">
-        <v>4003</v>
+        <v>4144</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="2" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>108</v>
@@ -3906,20 +3888,20 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A74" s="5">
-        <v>4007</v>
+        <v>4504</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>2</v>
@@ -3930,20 +3912,20 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A75" s="5">
-        <v>4010</v>
+        <v>4507</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="2" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>2</v>
@@ -3954,20 +3936,20 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A76" s="5">
-        <v>4011</v>
+        <v>4508</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="2" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>2</v>
@@ -3978,20 +3960,20 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A77" s="5">
-        <v>4016</v>
+        <v>4513</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>2</v>
@@ -4002,20 +3984,20 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A78" s="5">
-        <v>4040</v>
+        <v>4536</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="2" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>2</v>
@@ -4026,20 +4008,20 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A79" s="5">
-        <v>4043</v>
+        <v>4537</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="2" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>2</v>
@@ -4050,20 +4032,20 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A80" s="5">
-        <v>4044</v>
+        <v>5718</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="2" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>2</v>
@@ -4074,20 +4056,20 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A81" s="5">
-        <v>4049</v>
+        <v>5721</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="2" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>2</v>
@@ -4098,20 +4080,20 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A82" s="5">
-        <v>4144</v>
+        <v>5722</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="2" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>2</v>
@@ -4122,17 +4104,17 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A83" s="5">
-        <v>4504</v>
+        <v>5727</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>1</v>
@@ -4147,17 +4129,17 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A84" s="5">
-        <v>4507</v>
+        <v>5793</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="2" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>1</v>
@@ -4172,17 +4154,17 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A85" s="5">
-        <v>4508</v>
+        <v>13762</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>1</v>
@@ -4195,21 +4177,21 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A86" s="5">
-        <v>4513</v>
+      <c r="A86" s="2">
+        <v>190</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="2" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>2</v>
@@ -4219,48 +4201,48 @@
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A87" s="5">
-        <v>4536</v>
+      <c r="A87" s="2">
+        <v>1344</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="2" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>139</v>
+        <v>182</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H87" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A88" s="5">
-        <v>4537</v>
+      <c r="A88" s="2">
+        <v>1346</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="2" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>141</v>
+        <v>183</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H88" s="5">
         <v>3</v>
@@ -4268,24 +4250,24 @@
       <c r="I88" s="4"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A89" s="5">
-        <v>5718</v>
+      <c r="A89" s="2">
+        <v>1347</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="2" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H89" s="5">
         <v>3</v>
@@ -4293,47 +4275,47 @@
       <c r="I89" s="4"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A90" s="5">
-        <v>5721</v>
+      <c r="A90" s="2">
+        <v>1355</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="2" t="s">
-        <v>148</v>
+        <v>191</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H90" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A91" s="5">
-        <v>5722</v>
-      </c>
-      <c r="B91" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C91" s="11"/>
-      <c r="D91" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G91" s="2" t="s">
+      <c r="A91" s="1">
+        <v>1402</v>
+      </c>
+      <c r="B91" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="12"/>
+      <c r="D91" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H91" s="5">
@@ -4341,23 +4323,23 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A92" s="5">
-        <v>5727</v>
-      </c>
-      <c r="B92" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C92" s="11"/>
-      <c r="D92" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G92" s="2" t="s">
+      <c r="A92" s="1">
+        <v>1403</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="12"/>
+      <c r="D92" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G92" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H92" s="5">
@@ -4365,23 +4347,23 @@
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A93" s="5">
-        <v>5793</v>
-      </c>
-      <c r="B93" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C93" s="11"/>
-      <c r="D93" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G93" s="2" t="s">
+      <c r="A93" s="1">
+        <v>1404</v>
+      </c>
+      <c r="B93" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="12"/>
+      <c r="D93" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="G93" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H93" s="5">
@@ -4389,21 +4371,21 @@
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A94" s="5">
-        <v>13762</v>
+      <c r="A94" s="2">
+        <v>1455</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="2" t="s">
-        <v>144</v>
+        <v>192</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>2</v>
@@ -4413,23 +4395,23 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A95" s="2">
-        <v>190</v>
-      </c>
-      <c r="B95" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C95" s="11"/>
-      <c r="D95" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="F95" s="2" t="s">
+      <c r="A95" s="1">
+        <v>4466</v>
+      </c>
+      <c r="B95" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="12"/>
+      <c r="D95" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="G95" s="2" t="s">
+      <c r="G95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H95" s="5">
@@ -4437,24 +4419,24 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="A96" s="2">
-        <v>1344</v>
+      <c r="A96" s="5">
+        <v>7326</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="2" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="H96" s="5">
         <v>3</v>
@@ -4462,94 +4444,94 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A97" s="2">
-        <v>1346</v>
+        <v>20105</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H97" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A98" s="2">
-        <v>1347</v>
+      <c r="A98" s="5">
+        <v>24364</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="2" t="s">
-        <v>190</v>
+        <v>28</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="F98" s="2">
+        <v>0</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H98" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A99" s="2">
-        <v>1355</v>
+      <c r="A99" s="5">
+        <v>24369</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="2" t="s">
-        <v>191</v>
+        <v>9</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>185</v>
+        <v>10</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H99" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A100" s="1">
-        <v>1402</v>
-      </c>
-      <c r="B100" s="12" t="s">
+      <c r="A100" s="5">
+        <v>24382</v>
+      </c>
+      <c r="B100" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C100" s="12"/>
-      <c r="D100" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="G100" s="1" t="s">
+      <c r="C100" s="11"/>
+      <c r="D100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H100" s="5">
@@ -4558,20 +4540,20 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>1403</v>
+        <v>28484</v>
       </c>
       <c r="B101" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C101" s="12"/>
       <c r="D101" s="1" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>247</v>
+        <v>7</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>2</v>
@@ -4581,23 +4563,23 @@
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A102" s="1">
-        <v>1404</v>
-      </c>
-      <c r="B102" s="12" t="s">
+      <c r="A102" s="5">
+        <v>28503</v>
+      </c>
+      <c r="B102" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C102" s="12"/>
-      <c r="D102" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="G102" s="1" t="s">
+      <c r="C102" s="11"/>
+      <c r="D102" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G102" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H102" s="5">
@@ -4605,18 +4587,18 @@
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A103" s="2">
-        <v>1455</v>
+      <c r="A103" s="5">
+        <v>28509</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C103" s="11"/>
       <c r="D103" s="2" t="s">
-        <v>192</v>
+        <v>94</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>7</v>
@@ -4629,23 +4611,23 @@
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A104" s="1">
-        <v>4466</v>
-      </c>
-      <c r="B104" s="12" t="s">
+      <c r="A104" s="5">
+        <v>28511</v>
+      </c>
+      <c r="B104" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C104" s="12"/>
-      <c r="D104" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="G104" s="1" t="s">
+      <c r="C104" s="11"/>
+      <c r="D104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H104" s="5">
@@ -4654,44 +4636,44 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A105" s="5">
-        <v>7326</v>
+        <v>28763</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C105" s="11"/>
       <c r="D105" s="2" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="H105" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A106" s="2">
-        <v>20105</v>
+      <c r="A106" s="5">
+        <v>28770</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="2" t="s">
-        <v>193</v>
+        <v>101</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>2</v>
@@ -4701,48 +4683,48 @@
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A107" s="5">
-        <v>24364</v>
-      </c>
-      <c r="B107" s="11" t="s">
+      <c r="A107" s="1">
+        <v>22108</v>
+      </c>
+      <c r="B107" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C107" s="11"/>
-      <c r="D107" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F107" s="2">
-        <v>0</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>2</v>
+      <c r="C107" s="12"/>
+      <c r="D107" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="H107" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A108" s="5">
-        <v>24369</v>
-      </c>
-      <c r="B108" s="11" t="s">
+      <c r="A108" s="1">
+        <v>22109</v>
+      </c>
+      <c r="B108" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C108" s="11"/>
-      <c r="D108" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>2</v>
+      <c r="C108" s="12"/>
+      <c r="D108" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="H108" s="5">
         <v>3</v>
@@ -4750,20 +4732,20 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A109" s="5">
-        <v>24382</v>
+        <v>28545</v>
       </c>
       <c r="B109" s="11" t="s">
         <v>8</v>
       </c>
       <c r="C109" s="11"/>
       <c r="D109" s="2" t="s">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>2</v>
@@ -4773,24 +4755,24 @@
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A110" s="1">
-        <v>28484</v>
-      </c>
-      <c r="B110" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="12"/>
-      <c r="D110" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>2</v>
+      <c r="A110" s="5">
+        <v>13521</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C110" s="11"/>
+      <c r="D110" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="H110" s="5">
         <v>3</v>
@@ -4798,140 +4780,152 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A111" s="5">
-        <v>28503</v>
+        <v>606</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C111" s="11"/>
+        <v>323</v>
+      </c>
+      <c r="C111" s="11" t="s">
+        <v>318</v>
+      </c>
       <c r="D111" s="2" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H111" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A112" s="5">
-        <v>28509</v>
+        <v>619</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C112" s="11"/>
+        <v>323</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>318</v>
+      </c>
       <c r="D112" s="2" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H112" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A113" s="5">
-        <v>28511</v>
+        <v>632</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C113" s="11"/>
+        <v>323</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>318</v>
+      </c>
       <c r="D113" s="2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H113" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A114" s="5">
-        <v>28763</v>
+        <v>645</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C114" s="11"/>
+        <v>323</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>318</v>
+      </c>
       <c r="D114" s="2" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H114" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A115" s="5">
-        <v>28770</v>
+        <v>918</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115" s="11"/>
+        <v>323</v>
+      </c>
+      <c r="C115" s="11" t="s">
+        <v>318</v>
+      </c>
       <c r="D115" s="2" t="s">
-        <v>101</v>
+        <v>54</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>102</v>
+        <v>55</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H115" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A116" s="5">
-        <v>3698</v>
+        <v>931</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C116" s="11"/>
+        <v>323</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>318</v>
+      </c>
       <c r="D116" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>177</v>
+        <v>56</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>178</v>
+        <v>47</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>2</v>
@@ -4942,20 +4936,22 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A117" s="5">
-        <v>11752</v>
+        <v>944</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C117" s="11"/>
+        <v>323</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>318</v>
+      </c>
       <c r="D117" s="2" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>2</v>
@@ -4965,23 +4961,25 @@
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A118" s="1">
-        <v>22704</v>
-      </c>
-      <c r="B118" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C118" s="12"/>
-      <c r="D118" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="G118" s="1" t="s">
+      <c r="A118" s="5">
+        <v>957</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H118" s="5">
@@ -4989,23 +4987,25 @@
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A119" s="1">
-        <v>22705</v>
-      </c>
-      <c r="B119" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C119" s="12"/>
-      <c r="D119" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="G119" s="1" t="s">
+      <c r="A119" s="5">
+        <v>3986</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="C119" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G119" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H119" s="5">
@@ -5013,23 +5013,23 @@
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A120" s="1">
-        <v>22706</v>
-      </c>
-      <c r="B120" s="12" t="s">
+      <c r="A120" s="5">
+        <v>3698</v>
+      </c>
+      <c r="B120" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C120" s="12"/>
-      <c r="D120" s="1" t="s">
-        <v>292</v>
+      <c r="C120" s="11"/>
+      <c r="D120" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="G120" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="G120" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H120" s="5">
@@ -5037,23 +5037,23 @@
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A121" s="1">
-        <v>22707</v>
-      </c>
-      <c r="B121" s="12" t="s">
+      <c r="A121" s="5">
+        <v>11752</v>
+      </c>
+      <c r="B121" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C121" s="12"/>
-      <c r="D121" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="G121" s="1" t="s">
+      <c r="C121" s="11"/>
+      <c r="D121" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G121" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H121" s="5">
@@ -5062,17 +5062,17 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>22708</v>
+        <v>22704</v>
       </c>
       <c r="B122" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C122" s="12"/>
       <c r="D122" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>262</v>
@@ -5086,17 +5086,17 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>22709</v>
+        <v>22705</v>
       </c>
       <c r="B123" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C123" s="12"/>
       <c r="D123" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>262</v>
@@ -5108,48 +5108,48 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A124" s="2">
-        <v>23461</v>
-      </c>
-      <c r="B124" s="11" t="s">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A124" s="1">
+        <v>22706</v>
+      </c>
+      <c r="B124" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C124" s="11"/>
-      <c r="D124" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>85</v>
+      <c r="C124" s="12"/>
+      <c r="D124" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="H124" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A125" s="5">
-        <v>27841</v>
-      </c>
-      <c r="B125" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C125" s="11"/>
-      <c r="D125" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F125" s="2">
-        <v>0</v>
-      </c>
-      <c r="G125" s="2" t="s">
+      <c r="A125" s="1">
+        <v>22707</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C125" s="12"/>
+      <c r="D125" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="G125" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H125" s="5">
@@ -5158,20 +5158,20 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>21637</v>
+        <v>22708</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C126" s="12"/>
       <c r="D126" s="1" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>7</v>
+        <v>262</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>2</v>
@@ -5182,71 +5182,71 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>22105</v>
+        <v>22709</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C127" s="12"/>
       <c r="D127" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>7</v>
+        <v>262</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H127" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A128" s="1">
-        <v>22106</v>
-      </c>
-      <c r="B128" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C128" s="12"/>
-      <c r="D128" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>27</v>
+    <row r="128" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="A128" s="2">
+        <v>23461</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C128" s="11"/>
+      <c r="D128" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="H128" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A129" s="1">
-        <v>22107</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C129" s="12"/>
-      <c r="D129" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>27</v>
+      <c r="A129" s="5">
+        <v>27841</v>
+      </c>
+      <c r="B129" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C129" s="11"/>
+      <c r="D129" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F129" s="2">
+        <v>0</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="H129" s="5">
         <v>4</v>
@@ -5254,41 +5254,41 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>22108</v>
+        <v>21637</v>
       </c>
       <c r="B130" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C130" s="12"/>
       <c r="D130" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H130" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>22109</v>
+        <v>22105</v>
       </c>
       <c r="B131" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C131" s="12"/>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>26</v>
+        <v>252</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>7</v>
@@ -5297,22 +5297,22 @@
         <v>27</v>
       </c>
       <c r="H131" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>22110</v>
+        <v>22106</v>
       </c>
       <c r="B132" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C132" s="12"/>
       <c r="D132" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>7</v>
@@ -5326,17 +5326,17 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>22111</v>
+        <v>22107</v>
       </c>
       <c r="B133" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C133" s="12"/>
       <c r="D133" s="1" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>7</v>
@@ -5350,17 +5350,17 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>22113</v>
+        <v>22110</v>
       </c>
       <c r="B134" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C134" s="12"/>
       <c r="D134" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>7</v>
@@ -5374,17 +5374,17 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>22114</v>
+        <v>22111</v>
       </c>
       <c r="B135" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C135" s="12"/>
       <c r="D135" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>7</v>
@@ -5398,17 +5398,17 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>22115</v>
+        <v>22113</v>
       </c>
       <c r="B136" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C136" s="12"/>
       <c r="D136" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>7</v>
@@ -5422,23 +5422,23 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>23982</v>
+        <v>22114</v>
       </c>
       <c r="B137" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C137" s="12"/>
       <c r="D137" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H137" s="5">
         <v>4</v>
@@ -5446,23 +5446,23 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>28473</v>
+        <v>22115</v>
       </c>
       <c r="B138" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C138" s="12"/>
       <c r="D138" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H138" s="5">
         <v>4</v>
@@ -5470,17 +5470,17 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>28478</v>
+        <v>23982</v>
       </c>
       <c r="B139" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C139" s="12"/>
       <c r="D139" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>7</v>
@@ -5494,17 +5494,17 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>28479</v>
+        <v>28473</v>
       </c>
       <c r="B140" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C140" s="12"/>
       <c r="D140" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>7</v>
@@ -5517,51 +5517,51 @@
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A141" s="5">
-        <v>28545</v>
-      </c>
-      <c r="B141" s="11" t="s">
+      <c r="A141" s="1">
+        <v>28478</v>
+      </c>
+      <c r="B141" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C141" s="11"/>
-      <c r="D141" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G141" s="2" t="s">
+      <c r="C141" s="12"/>
+      <c r="D141" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G141" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H141" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A142" s="5">
-        <v>13521</v>
-      </c>
-      <c r="B142" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C142" s="11"/>
-      <c r="D142" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>85</v>
+      <c r="A142" s="1">
+        <v>28479</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C142" s="12"/>
+      <c r="D142" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="H142" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
